--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1691,12 +1691,12 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Pass the evaluation</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>One phase, billed monthly, with no time limit and no minimum trading days.</t>
+          <t>Simulated account, real market data, billed monthly until you pass.</t>
         </is>
       </c>
     </row>
@@ -1706,17 +1706,17 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>funded</t>
+          <t>certification</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Choose LiveSim or Live</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>After you pass, you trade the same capital on a LiveSim or a Live account. The $139 activation fee is deducted from your first withdrawal.</t>
+          <t>No minimum days. Respect the target, the drawdown, the daily loss and the consistency rule.</t>
         </is>
       </c>
     </row>
@@ -1726,25 +1726,39 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
+          <t>funded</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Pick your account</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>The partner firm offers a LiveSim or a Live account with the same capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
           <t>payout</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Get paid weekly</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Withdrawals are processed every Wednesday, with a minimum net withdrawal of $100.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Payouts</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Request before Friday 2:00 PM CT, paid the following Wednesday, from $100.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n"/>
@@ -1873,34 +1887,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Training included</t>
-        </is>
-      </c>
+      <c r="A3" s="16" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>element</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Video library and study guides, free during the evaluation.</t>
-        </is>
-      </c>
+      <c r="A4" s="16" t="n"/>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n"/>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Trade with simulated capital using real-time market data.</t>
+          <t>Simulated capital, real market data, real withdrawals.</t>
         </is>
       </c>
       <c r="C3" s="23" t="n">
@@ -2061,12 +2055,12 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Accounts at the same time</t>
+          <t>Market data</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>Up to 3</t>
+          <t>Included in the $139 activation</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2072,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Trade with real capital and withdraw your profits.</t>
+          <t>Real capital, in a funded account at a partner firm.</t>
         </is>
       </c>
       <c r="C5" s="23" t="n">
@@ -2107,12 +2101,12 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Accounts at the same time</t>
+          <t>Market data</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>$140–156 per month per exchange</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2287,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>One-time, deducted from your first successful withdrawal. Nothing to pay upfront.</t>
+          <t>Deducted from your first withdrawal. Nothing to pay upfront.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n"/>
@@ -2304,7 +2298,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Evaluation reset</t>
+          <t>Reset (TCP25, TCP50)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -2314,7 +2308,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>On TCP25 and TCP50, always below the price of a new subscription. One free reset at each renewal.</t>
+          <t>Below the price of a new subscription. One free reset at each renewal.</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
@@ -2339,7 +2333,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>The schedule is given at activation and depends on the provider (Tradovate or Rithmic).</t>
+          <t>Schedule given at activation.</t>
         </is>
       </c>
       <c r="E5" s="16" t="n"/>
@@ -2559,7 +2553,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>All positions must be closed by 15:50 CT.</t>
+          <t>Close every position by 3:50 PM CT.</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -2569,11 +2563,7 @@
       </c>
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="17" t="n"/>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
+      <c r="G3" s="17" t="n"/>
       <c r="H3" s="17" t="n"/>
       <c r="I3" s="17" t="inlineStr">
         <is>
@@ -2582,7 +2572,7 @@
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>https://help.earn2trade.com/en/articles/2090496-can-i-hold-positions-overnight-on-the-trader-career-path-gauntlet-mini</t>
+          <t>https://help.earn2trade.com/en/articles/6877364-what-happens-when-i-complete-my-evaluation</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2589,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Not allowed: positions cannot be held overnight.</t>
+          <t>Not allowed.</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
@@ -2609,11 +2599,7 @@
       </c>
       <c r="E4" s="17" t="n"/>
       <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
+      <c r="G4" s="17" t="n"/>
       <c r="H4" s="17" t="n"/>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -2622,7 +2608,7 @@
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>https://help.earn2trade.com/en/articles/2090496-can-i-hold-positions-overnight-on-the-trader-career-path-gauntlet-mini</t>
+          <t>https://help.earn2trade.com/en/articles/6877364-what-happens-when-i-complete-my-evaluation</t>
         </is>
       </c>
     </row>
@@ -2687,11 +2673,7 @@
       <c r="F6" s="16" t="n"/>
       <c r="G6" s="16" t="n"/>
       <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I6" s="16" t="n"/>
       <c r="J6" s="16" t="inlineStr">
         <is>
           <t>https://help.earn2trade.com/en/articles/2090521-what-platforms-can-i-use-for-the-gauntlet-mini-trader-career-path</t>
@@ -2779,7 +2761,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>The split depends on the size of each withdrawal, not on accumulated profit.</t>
+          <t>Based on the size of each withdrawal, not on total profit.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -2819,7 +2801,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Processed every Wednesday. Request by email before 2:00 PM CT on the Friday before. Minimum net withdrawal: $100.</t>
+          <t>Every Wednesday. Request by 2:00 PM CT the Friday before. Minimum $100 net.</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -2854,12 +2836,12 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Withdrawal methods</t>
+          <t>Withdrawal fees</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>The firm chooses the provider. Rise: $50 per withdrawal outside the US, 1.5% in the US. Deel: $50. Bayzat: $5 to $40. Direct crypto: 0.735%, in select cases.</t>
+          <t>Rise $50 outside the US (1.5% in the US), Deel $50, Bayzat $5 to $40, direct crypto 0.735%. The firm picks the provider.</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -3277,11 +3259,7 @@
         </is>
       </c>
       <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I20" s="16" t="n"/>
       <c r="J20" s="16" t="inlineStr">
         <is>
           <t>https://help.earn2trade.com/en/articles/16295637-what-is-earn2trade</t>
@@ -3923,7 +3901,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Earn2Trade is rated 4.6 out of 5 on Trustpilot across nearly 5,000 reviews, and replies to 98% of negative reviews, usually within 48 hours. It also publishes its pass rate, which is still rare in the industry. The Trader Career Path suits traders who would rather grow a small account than buy a large one outright. The trade-off is rules applied without flexibility: going over the allowed number of contracts ends the evaluation immediately, the drawdown becomes trailing on a Live account, and the profit split starts at 50%. Choose it if you are disciplined and patient; avoid it if you want a 90% split from the first dollar or forgiving rules.</t>
+          <t>A good fit for disciplined traders who would rather grow a small account step by step than buy a large one outright, from a firm that publishes its pass rate, which is still rare. The trade-off is strict rules with little room for error. Look elsewhere if you want a high split from the first dollar.</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3976,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Monthly subscription. On the Trader Career Path, each renewal includes a free reset.</t>
+          <t>Going over the contract limit of the progression ladder ends the evaluation immediately. Ten micro contracts count as one.</t>
         </is>
       </c>
     </row>
@@ -4013,7 +3991,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>No swing trading in the evaluation: every position must be closed by 15:50 Chicago time.</t>
+          <t>Funded split: 50% below a threshold that depends on the account size ($1,500 on TCP25), 80% above it.</t>
         </is>
       </c>
     </row>
@@ -4028,99 +4006,39 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>30% consistency rule during the evaluation, removed once funded.</t>
+          <t>Citizens of 25 countries cannot be funded, including Nigeria, Pakistan, Kenya, Ukraine and Russia.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Progression ladder: the number of contracts allowed depends on your balance, and going over it ends the evaluation immediately. Ten micro contracts count as one standard contract.</t>
-        </is>
-      </c>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Funded profit split: 50% below a threshold that depends on the account size ($1,500 on TCP25, $2,250 on TCP50, $3,000 on TCP100), 80% above it.</t>
-        </is>
-      </c>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Drawdown: end of day in the evaluation and on LiveSim, trailing on a Live account.</t>
-        </is>
-      </c>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Most funded traders stay on simulated capital: in 2025, 5.23% of successful traders traded a Live account and 94.77% a LiveSim account.</t>
-        </is>
-      </c>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Futures only: no stocks, options, forex, crypto or CFDs.</t>
-        </is>
-      </c>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Citizens of 25 countries cannot be funded, including Nigeria, Pakistan, Kenya, Ukraine and Russia.</t>
-        </is>
-      </c>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n"/>
@@ -4420,7 +4338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4766,6 +4684,11 @@
           <t>needs_confirmation</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>certification</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>crypto</t>
@@ -4784,6 +4707,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4981,7 +4905,7 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Earn2Trade review: Trader Career Path rules and prices (2026)</t>
+          <t>A structured path to a funded futures account</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -5003,7 +4927,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Futures prop firm: the Trader Career Path grows from $25K to $200K, with an end-of-day drawdown in the evaluation, a profit split of up to 80% and weekly payouts.</t>
+          <t>Choose between climbing to $400K or funding your target size straight away. Single-step evaluation, no minimum trading days, weekly payouts.</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -5535,64 +5459,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>passed the evaluation in 2025</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>8.89%</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>https://www.earn2trade.com/non-us/trader-career-path</t>
-        </is>
-      </c>
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>of Live accounts had a withdrawal in 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>18.04%</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>https://www.earn2trade.com/non-us/trader-career-path</t>
-        </is>
-      </c>
+      <c r="A4" s="23" t="n"/>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>of LiveSim accounts had a withdrawal in 2025</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>18.20%</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>https://www.earn2trade.com/non-us/trader-career-path</t>
-        </is>
-      </c>
+      <c r="A5" s="23" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n"/>
@@ -5637,12 +5519,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5661,6 +5544,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -5678,6 +5566,11 @@
           <t>Pourquoi, d'ou vient le nom. Non affiche.</t>
         </is>
       </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle, prise sur le site de l'editeur (https). Vide : pastille a l'initiale.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
@@ -5695,6 +5588,11 @@
           <t>Free during the evaluation (help centre, article 2090521).</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://ninjatrader.com/assets/dist/images/favicons/apple-touch-icon.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
@@ -5729,6 +5627,11 @@
           <t>Free during the evaluation (help centre, article 2090521).</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.rithmic.com/favicon.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -5761,6 +5664,11 @@
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Free during the evaluation (help centre, article 2090521).</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://static.tradingview.com/static/images/favicon/apple-touch-icon-180x180.png</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6123,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="17" t="n"/>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Start smaller, climb higher</t>
+        </is>
+      </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Start at $25K, $50K or $100K, then move up step by step to a $200K Live account.</t>
@@ -6255,7 +6167,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F4" s="16" t="n"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Start at your target size</t>
+        </is>
+      </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
           <t>A single-phase evaluation at the account size you want, from $50K to $200K.</t>
@@ -6600,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L153"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6615,6 +6531,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6678,6 +6595,11 @@
           <t>controle  (auto)</t>
         </is>
       </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>lien_plan</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6738,6 +6660,11 @@
       <c r="L2" s="25" t="inlineStr">
         <is>
           <t>ok, ou ce qui manque.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10124,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H4" s="22" t="n">
@@ -10299,7 +10226,7 @@
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H6" s="21" t="n">
@@ -10401,7 +10328,7 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H8" s="21" t="n">
@@ -10503,7 +10430,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H10" s="21" t="n">
@@ -10605,7 +10532,7 @@
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H12" s="21" t="n">
@@ -10707,7 +10634,7 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H14" s="21" t="n">
@@ -10809,7 +10736,7 @@
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>End of Day on LiveSim, trailing on Live</t>
+          <t>EOD on LiveSim, trailing on Live</t>
         </is>
       </c>
       <c r="H16" s="21" t="n">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Reset (TCP25, TCP50)</t>
+          <t>Reset (TCP25, TCP50, GM 50K)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -2308,14 +2308,10 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Below the price of a new subscription. One free reset at each renewal.</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>tcp</t>
-        </is>
-      </c>
+          <t>Below the price of a new subscription. The Trader Career Path adds one free reset at each renewal.</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="23" t="n">
@@ -2328,12 +2324,12 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Per instrument</t>
+          <t>Per contract</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Schedule given at activation.</t>
+          <t>Once funded, per contract and per side: about $0.54 exchange fee ($0.46 on micros), $0.10 Rithmic, $0.02 NFA, plus platform fees.</t>
         </is>
       </c>
       <c r="E5" s="16" t="n"/>
@@ -2421,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3239,7 +3235,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>After you withdraw your profit goal minus 20%, you move to the next Live account: $50K, then $100K, then $200K. The help center says the plan can grow up to $400,000.</t>
+          <t>Withdraw your profit goal minus 20% to move up: $50K, $100K, then $200K Live, on a fixed $194,000 floor.</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -3252,7 +3248,11 @@
           <t>tcp</t>
         </is>
       </c>
-      <c r="F20" s="16" t="n"/>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
           <t>funded</t>
@@ -3262,7 +3262,7 @@
       <c r="I20" s="16" t="n"/>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>https://help.earn2trade.com/en/articles/16295637-what-is-earn2trade</t>
+          <t>Handbook partenaire Earn2Trade 2026 (fourni par Sofiane)</t>
         </is>
       </c>
     </row>
@@ -3303,52 +3303,168 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Moving up the Trader Career Path</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Withdraw your profit goal minus 20% to move up, all the way to $400K Live: fixed $388,000 floor and a fixed 60/40 split.</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>50000, 100000</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
+      </c>
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>Handbook partenaire Earn2Trade 2026 (fourni par Sofiane)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>trading</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>End-of-day drawdown</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>The floor only moves up at the close, but open losses count in real time: dipping below it during the day fails the account.</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E23" s="16" t="n"/>
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>https://help.earn2trade.com/en/articles/5372687-how-does-end-of-day-drawdown-work</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>trading</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Trade copiers</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Not allowed.</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E24" s="16" t="n"/>
       <c r="F24" s="16" t="n"/>
       <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>https://help.earn2trade.com/en/articles/6877364-what-happens-when-i-complete-my-evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>payouts</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Keep a cushion</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Once the floor locks at your starting balance, withdrawing all your profit leaves no margin. Leave a buffer in the account.</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="E25" s="16" t="n"/>
       <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
+      </c>
       <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Handbook partenaire Earn2Trade 2026 (fourni par Sofiane)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n"/>
@@ -3818,6 +3934,7 @@
       <c r="I64" s="16" t="n"/>
       <c r="J64" s="16" t="n"/>
     </row>
+    <row r="65"/>
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
@@ -4338,7 +4455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4707,7 +4824,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6130,7 +6246,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>Start at $25K, $50K or $100K, then move up step by step to a $200K Live account.</t>
+          <t>Start at $25K, $50K or $100K and move up step by step: to $200K from TCP25, to $400K from TCP50 and TCP100.</t>
         </is>
       </c>
       <c r="H3" s="24" t="n"/>
@@ -6863,7 +6979,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="I7" s="29" t="n"/>
+      <c r="I7" s="29" t="n">
+        <v>100</v>
+      </c>
       <c r="J7" s="29" t="n"/>
       <c r="K7" s="26">
         <f>IF(A7="","",SUMPRODUCT((Phases!$A$3:$A$900=A7)*(Phases!$B$3:$B$900=B7)*(Phases!$C$3:$C$900=C7)))</f>
@@ -6903,7 +7021,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="I8" s="29" t="n"/>
+      <c r="I8" s="29" t="n">
+        <v>130</v>
+      </c>
       <c r="J8" s="29" t="n"/>
       <c r="K8" s="26">
         <f>IF(A8="","",SUMPRODUCT((Phases!$A$3:$A$900=A8)*(Phases!$B$3:$B$900=B8)*(Phases!$C$3:$C$900=C8)))</f>
@@ -6943,7 +7063,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="I9" s="29" t="n"/>
+      <c r="I9" s="29" t="n">
+        <v>155</v>
+      </c>
       <c r="J9" s="29" t="n"/>
       <c r="K9" s="26">
         <f>IF(A9="","",SUMPRODUCT((Phases!$A$3:$A$900=A9)*(Phases!$B$3:$B$900=B9)*(Phases!$C$3:$C$900=C9)))</f>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1887,19 +1887,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n"/>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="16" t="n"/>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Training included once you buy:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n"/>
-      <c r="B4" s="23" t="n"/>
-      <c r="C4" s="16" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Video library</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="16" t="n"/>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Study guides</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n"/>
@@ -2034,12 +2064,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Drawdown</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>End of day</t>
+          <t>Right after you pass</t>
         </is>
       </c>
     </row>
@@ -2055,19 +2085,19 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Market data</t>
+          <t>Drawdown</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>Included in the $139 activation</t>
+          <t>End of day</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>LiveSim</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -2076,16 +2106,16 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Drawdown</t>
+          <t>Market data</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Included in the $139 activation</t>
         </is>
       </c>
     </row>
@@ -2095,34 +2125,66 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Real capital, in a funded account at a partner firm.</t>
+        </is>
+      </c>
       <c r="C6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Up to 10 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Drawdown</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Trailing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Market data</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>$140–156 per month per exchange</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -2417,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3267,40 +3329,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>trading</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Data feed</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Chosen at purchase: Rithmic (Finamark, R Trader Pro), BlackArrow, or NinjaTrader (Tradovate, TradingView).</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
       <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
+      <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>https://www.earn2trade.com/non-us/purchase</t>
-        </is>
-      </c>
+      <c r="J21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -3934,7 +3972,6 @@
       <c r="I64" s="16" t="n"/>
       <c r="J64" s="16" t="n"/>
     </row>
-    <row r="65"/>
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
@@ -4318,10 +4355,14 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Is [Firm] suitable for beginners?</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="n"/>
+          <t>Is Earn2Trade legit?</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Earn2Trade is an education and evaluation company based in Wyoming, founded in 2016. It runs simulated evaluations, and traders who pass are funded by partner proprietary trading firms. It also publishes its pass rate. Review the rules carefully and consider starting with a smaller account.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="n">
@@ -4329,10 +4370,14 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>How much does [Firm] cost?</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
+          <t>How much does Earn2Trade cost?</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Evaluations are billed monthly, from $150 to $550 per month depending on the program and account size. The subscription renews every 30 days until you pass or cancel, so budget for more than one cycle. The configurator above shows the exact price of each program and size.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="23" t="n">
@@ -4340,10 +4385,14 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>What profit split does [Firm] offer?</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
+          <t>What profit split does Earn2Trade offer?</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>The split depends on the size of each withdrawal: 50% below a threshold that depends on the account size ($1,500 on TCP25, $2,250 on TCP50 and GM 50K), 80% above it. The $400K Trader Career Path tier pays a fixed 60/40.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n">
@@ -4351,10 +4400,14 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>How do payouts work?</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n"/>
+          <t>Can I trade the news or hold positions overnight?</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>News trading is allowed. Every position must be closed by 3:50 PM CT: no overnight or weekend holding, in the evaluation and once funded. Trade copiers are not allowed.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n">
@@ -4362,20 +4415,44 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Does the promotional code apply to every account?</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n"/>
+          <t>How does Earn2Trade handle payouts?</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Payouts are processed every Wednesday for requests sent before 2:00 PM CT on the previous Friday. The minimum is $100 net, paid through Rise, Deel, Bayzat or, in some cases, direct crypto. There are no minimum trading days before a withdrawal.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
+      <c r="A8" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>What fees are deducted from the first withdrawal?</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Nothing is paid upfront. On a LiveSim account, a one-time $139 activation fee is deducted from your first profitable withdrawal, and never charged if you make no withdrawal. A Live account has no activation fee but pays market data: $140 per month per exchange with Rithmic, $156 with NinjaTrader. The monthly subscription stops once you pass.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
+      <c r="A9" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>What is the maximum capital I can manage at Earn2Trade?</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Up to $400K by climbing the Trader Career Path from TCP50 or TCP100, and up to $200K from TCP25. You can run up to 5 evaluations and 3 funded accounts at a time, only one of them Live.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n"/>
@@ -4836,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5105,7 +5182,9 @@
           <t>annee_creation</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
+      <c r="B13" s="23" t="n">
+        <v>2016</v>
+      </c>
       <c r="C13" s="24" t="n">
         <v>2024</v>
       </c>
@@ -5187,7 +5266,11 @@
           <t>categories_actifs</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Index futures, Energy futures, Metals futures, Agricultural futures, Currency futures, Micro futures</t>
+        </is>
+      </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
           <t>(vide — non confirmees)</t>
@@ -5205,7 +5288,11 @@
           <t>categories_actifs_statut</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
           <t>needs_confirmation</t>
@@ -5362,6 +5449,20 @@
       <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5802,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Liste validee par Sofiane le 22/09/2026 ; logo : icone du site officiel de l'editeur.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5713,7 +5814,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Finamark</t>
+          <t>Tradovate</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -5723,14 +5824,19 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Liste validee par Sofiane le 22/09/2026. Logo : icone de l'application web officielle (le favicon du site refuse l'affichage ailleurs).</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://trader.tradovate.com/img/icons/iphone-retina.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>R | Trader Pro</t>
+          <t>Rithmic</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -5740,7 +5846,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Liste validee par Sofiane le 22/09/2026 ; logo : icone du site officiel de l'editeur.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5752,7 +5858,7 @@
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Tradovate</t>
+          <t>Quantower</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -5762,7 +5868,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Liste validee par Sofiane le 22/09/2026 ; logo : icone du site officiel de l'editeur.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.quantower.com/favicon.ico</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5890,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Liste validee par Sofiane le 22/09/2026 ; logo : icone du site officiel de l'editeur.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5791,24 +5902,24 @@
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>BlackArrow One</t>
+          <t>Finamark</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Free during the evaluation (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Quantower</t>
+          <t>BlackArrow One</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -5818,7 +5929,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5946,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5963,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5980,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5997,7 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5903,7 +6014,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5920,7 +6031,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5937,7 +6048,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6065,7 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5971,7 +6082,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6099,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6116,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6133,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6150,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6167,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Usable with your own licence (help centre, article 2090521).</t>
+          <t>Also usable (help centre, article 2090521).</t>
         </is>
       </c>
     </row>
@@ -18674,7 +18785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18683,6 +18794,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -18716,6 +18828,11 @@
           <t>programmes</t>
         </is>
       </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -18748,30 +18865,110 @@
           <t>Slugs concernes, separes par des virgules. Vide : tous les programmes.</t>
         </is>
       </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle de l'option, prise sur le site de l'editeur (https). Vide : logo de la plateforme du meme nom, sinon initiale.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n"/>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>data_feed</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Rithmic</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Finamark, R Trader Pro</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>rithmic</t>
+        </is>
+      </c>
       <c r="F3" s="16" t="n"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.rithmic.com/favicon.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n"/>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>data_feed</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>BlackArrow</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Newest feed, added 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>blackarrow</t>
+        </is>
+      </c>
       <c r="F4" s="16" t="n"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://play-lh.googleusercontent.com/191WjA_sl5t4IRzwv6dVF8R-8zgkPsfyLJoT1y3lhHRh4uhopEvvoXycxFrEeaXxn3ViFJ6MszdgoVLAVPxgQg=w180-h180</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>data_feed</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>NinjaTrader</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Tradovate, TradingView</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>ninjatrader</t>
+        </is>
+      </c>
       <c r="F5" s="16" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://ninjatrader.com/assets/dist/images/favicons/apple-touch-icon.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n"/>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -6743,7 +6743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6759,6 +6759,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6827,6 +6828,11 @@
           <t>lien_plan</t>
         </is>
       </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>devise_compte</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6892,6 +6898,11 @@
       <c r="M2" s="25" t="inlineStr">
         <is>
           <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>Devise du SOLDE du compte : la taille, l'objectif et les limites. Vide : la devise du prix. A remplir quand la firme facture dans une monnaie et libelle les comptes dans une autre.</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -2479,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2545,6 +2545,11 @@
           <t>source_url</t>
         </is>
       </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>variantes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -2595,6 +2600,11 @@
       <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Page officielle. Non affichee.</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
+        <is>
+          <t>Variantes concernees (Day Trade, Swing, NEW...), separees par des virgules. Vide : toutes.</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6266,6 +6276,16 @@
           <t>nb_plans  (auto)</t>
         </is>
       </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin_statut</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -6321,6 +6341,16 @@
       <c r="K2" s="25" t="inlineStr">
         <is>
           <t>Plans rattaches.</t>
+        </is>
+      </c>
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t>Campagne a duree limitee : sa date de fin. Vide si le programme est permanent.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed si la date est publiee. Sinon not_published, needs_confirmation ou source_conflict.</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>0.3</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>non_confirmee</t>
+          <t>universelle_verifiee</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -1471,7 +1471,11 @@
           <t>expire_le</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-01T05:00:00+00:00</t>
+        </is>
+      </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
           <t>(vide — date de fin inconnue)</t>
@@ -2397,10 +2401,24 @@
       <c r="E5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
+      <c r="A6" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>End of September offer</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>-60% for 3 months</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50%, on the first three monthly billings. Resets are cheaper over the same three months: $55 on TCP25, $65 on TCP50, $60 on GAU50. After that, the code returns to 50% on every billing.</t>
+        </is>
+      </c>
       <c r="E6" s="16" t="n"/>
     </row>
     <row r="7">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,23 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>60% off the first three months, and the free reset stays</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>0.3</v>
@@ -1471,11 +1471,7 @@
           <t>expire_le</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>2026-10-01T05:00:00+00:00</t>
-        </is>
-      </c>
+      <c r="B8" s="32" t="n"/>
       <c r="C8" s="33" t="inlineStr">
         <is>
           <t>(vide — date de fin inconnue)</t>
@@ -1523,6 +1519,38 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>remise_campagne</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>campagne_fin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-01T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60% off the first three months, and the free reset stays</t>
+          <t>60% off + a free reset with every evaluation. Ends Sep 30.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60% off + a free reset with every evaluation. Ends Sep 30.</t>
+          <t>Plus a free reset with every evaluation — until Sep 30.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>-60% for 3 months</t>
+          <t>-60% + free reset</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50%, on the first three monthly billings. Resets are cheaper over the same three months: $55 on TCP25, $65 on TCP50, $60 on GAU50. After that, the code returns to 50% on every billing.</t>
+          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50%, on the first three monthly billings, and every evaluation comes with a free reset. Reset prices over the same three months: $55 on TCP25, $65 on TCP50, $60 on GAU50. After that, the code returns to 50% on every billing.</t>
         </is>
       </c>
       <c r="E6" s="16" t="n"/>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plus a free reset with every evaluation — until Sep 30.</t>
+          <t>One free reset comes with it: a second attempt, nothing more to pay. Until Sep 30.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>-60% + free reset</t>
+          <t>-60% + 1 free reset</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50%, on the first three monthly billings, and every evaluation comes with a free reset. Reset prices over the same three months: $55 on TCP25, $65 on TCP50, $60 on GAU50. After that, the code returns to 50% on every billing.</t>
+          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50% on the first three monthly billings. Every evaluation bought before the deadline also comes with one free reset: fail it, restart it, nothing more to pay. Any further reset costs $55 on TCP25, $65 on TCP50, $60 on GAU50 over the same three months. After that, the code returns to 50% on every billing.</t>
         </is>
       </c>
       <c r="E6" s="16" t="n"/>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1551,6 +1551,23 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>+1 free reset</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>One free reset comes with it: a second attempt, nothing more to pay. Until Sep 30.</t>
+          <t>Flash offer — free reset included. Until Sep 30 only.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -7059,6 +7059,11 @@
         <f>IF(A3="","",IF(COUNTIF(Programmes!$A$3:$A$60,A3)=0,"programme inconnu",IF(K3=0,"aucune phase","ok")))</f>
         <v/>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>earn2trade-tcp25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -7099,6 +7104,11 @@
         <f>IF(A4="","",IF(COUNTIF(Programmes!$A$3:$A$60,A4)=0,"programme inconnu",IF(K4=0,"aucune phase","ok")))</f>
         <v/>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>earn2trade-tcp50</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -7140,6 +7150,11 @@
       <c r="L5" s="28">
         <f>IF(A5="","",IF(COUNTIF(Programmes!$A$3:$A$60,A5)=0,"programme inconnu",IF(K5=0,"aucune phase","ok")))</f>
         <v/>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>earn2trade-tcp100</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -7181,6 +7196,11 @@
         <f>IF(A6="","",IF(COUNTIF(Programmes!$A$3:$A$60,A6)=0,"programme inconnu",IF(K6=0,"aucune phase","ok")))</f>
         <v/>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>earn2trade-gm50</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -7223,6 +7243,11 @@
         <f>IF(A7="","",IF(COUNTIF(Programmes!$A$3:$A$60,A7)=0,"programme inconnu",IF(K7=0,"aucune phase","ok")))</f>
         <v/>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>earn2trade-gm100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -7265,6 +7290,11 @@
         <f>IF(A8="","",IF(COUNTIF(Programmes!$A$3:$A$60,A8)=0,"programme inconnu",IF(K8=0,"aucune phase","ok")))</f>
         <v/>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>earn2trade-gm150</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -7306,6 +7336,11 @@
       <c r="L9" s="28">
         <f>IF(A9="","",IF(COUNTIF(Programmes!$A$3:$A$60,A9)=0,"programme inconnu",IF(K9=0,"aucune phase","ok")))</f>
         <v/>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>earn2trade-gm200</t>
+        </is>
       </c>
     </row>
     <row r="10">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Flash offer — free reset included. Until Sep 30 only.</t>
+          <t>Earn2Trade turns 10: anniversary offers until 18 October.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -1528,9 +1528,6 @@
           <t>remise_campagne</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.6</v>
-      </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
@@ -1543,11 +1540,6 @@
           <t>campagne_fin</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-01T05:00:00+00:00</t>
-        </is>
-      </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
@@ -1558,11 +1550,6 @@
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>bonus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>+1 free reset</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -2468,26 +2455,40 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>End of September offer</t>
+          <t>Anniversary pack</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>-60% + 1 free reset</t>
+          <t>$165 for three</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Until 30 September, end of day Central Time, code SCANNED takes 60% off instead of 50% on the first three monthly billings. Every evaluation bought before the deadline also comes with one free reset: fail it, restart it, nothing more to pay. Any further reset costs $55 on TCP25, $65 on TCP50, $60 on GAU50 over the same three months. After that, the code returns to 50% on every billing.</t>
+          <t>Until 10 October, three TCP25 evaluations and three resets for a single $165 payment — $27.50 per attempt. While stocks last.</t>
         </is>
       </c>
       <c r="E6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="A7" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Anniversary offer</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>-50% until 18 Oct</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>From 2 to 18 October, 50% off any Trader Career Path or Gauntlet Mini evaluation, and 50% off resets for the first 90 days.</t>
+        </is>
+      </c>
       <c r="E7" s="16" t="n"/>
     </row>
     <row r="8">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -17,15 +17,16 @@
     <sheet name="Phases" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OptionsAchat" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Offre" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conditions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Parcours" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Formation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ComptesApresReussite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Regles" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Verdict" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FAQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Listes" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="Campagnes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Conditions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parcours" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ComptesApresReussite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Couts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Verdict" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FAQ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Listes" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1511,11 +1512,6 @@
           <t>accroche</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Earn2Trade turns 10: anniversary offers until 18 October.</t>
-        </is>
-      </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
@@ -1578,6 +1574,419 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>remise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO d'ouverture. Avant elle, la campagne n'existe nulle part.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO de fermeture. Passee, la campagne disparait d'elle-meme.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots, pour la pastille : « Day 4 · -60% TCP25 ».</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Une phrase : ce que l'offre donne, telle qu'elle s'affiche.</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Taux pendant la fenetre, en %. Vide : le taux habituel de l'offre ne change pas.</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed pour s'afficher. Toute autre valeur la garde en reserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anniversary pack</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Three TCP25 evaluations and three resets for a single $165 payment — $27.50 per attempt, while stocks last.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-02T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-19T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10 years · -50%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50% off any Trader Career Path or Gauntlet Mini evaluation, and 50% off resets for the first 90 days.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-05T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-06T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Day 1 · resets -50%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50% off unlimited resets today, on every plan.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-07T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Day 2 · $50 coins</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>$50 in Discord Shop coins with your purchase today.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-08T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Day 3 · TCP25 -50%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>50% off the TCP25, and a funded $50K account once you pass.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-09T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Day 4 · TCP25 -60%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>60% off the TCP25 today, activation fee waived.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-10T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Day 5 · $100 coins</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>$100 in Discord Shop coins with your purchase today.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-13T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Day 6 · -60% 50K</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>60% off the TCP50 or the Gauntlet Mini 50K, plus a free evaluation after your first payout.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Day 7 · resets $45</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Flat $45 resets today, on every plan.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-15T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Day 8 · TCP100 -60%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>60% off the TCP100 today, with resets at $50.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-15T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-16T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Day 9 · free reset</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>50% off, and one free reset with every evaluation bought today.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-16T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-17T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Day 10 · finale -60%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Grand finale: 60% off any evaluation, and 50% off resets.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1673,7 +2082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1890,7 +2299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2030,7 +2439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2315,7 +2724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2553,7 +2962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -4086,7 +4495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4391,7 +4800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4616,7 +5025,581 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2937"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Champ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Valeur a remplir</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Exemple — FuturesElite, 7 sept. 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Ou ca s'affiche dans le HTML · si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>earn2trade</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Earn2Trade</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>https://www.earn2trade.com/apple-touch-icon.png</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_score</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_review_count</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>4995</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Nombre d'avis sous la note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/www.earn2trade.com</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>marches</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>A structured path to a funded futures account</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Choose between climbing to $400K or funding your target size straight away. Single-step evaluation, no minimum trading days, weekly payouts.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Earn2Trade is a US company specialised in futures. It runs the evaluation and the training, then connects successful traders with partner trading firms that provide the funded account.
+Its flagship program, the Trader Career Path, works like a ladder: you start with a $25,000 evaluation, and each goal you reach unlocks a larger account ($50K, $100K, then $200K).
+You trade only futures contracts listed on the CME, COMEX, NYMEX and CBOT, on around twenty platforms including NinjaTrader, Tradovate and TradingView. A training library is included.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>« Founded ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>pays</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Country ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>ceo_fondateur</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Osvaldo Guimarães</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>« CEO / Founder ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Futures</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Index futures, Energy futures, Metals futures, Agricultural futures, Currency futures, Micro futures</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>(vide — non confirmees)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs_statut</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>plateformes</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>methodes_retrait</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Rise, Deel, Bayzat, Direct crypto</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>prestataire_retrait</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>(vide — absent du releve)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Futures prop firm: Trader Career Path from $25K to $200K, end-of-day drawdown in the evaluation, split up to 80%, weekly payouts. Rules and pitfalls.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -4994,580 +5977,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F2937"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Champ</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Valeur a remplir</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Exemple — FuturesElite, 7 sept. 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Ou ca s'affiche dans le HTML · si vide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>earn2trade</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Earn2Trade</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>https://www.earn2trade.com/apple-touch-icon.png</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_score</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_review_count</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>4995</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Nombre d'avis sous la note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_url</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/www.earn2trade.com</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/exemple.com</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A structured path to a funded futures account</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Choose between climbing to $400K or funding your target size straight away. Single-step evaluation, no minimum trading days, weekly payouts.</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Earn2Trade is a US company specialised in futures. It runs the evaluation and the training, then connects successful traders with partner trading firms that provide the funded account.
-Its flagship program, the Trader Career Path, works like a ladder: you start with a $25,000 evaluation, and each goal you reach unlocks a larger account ($50K, $100K, then $200K).
-You trade only futures contracts listed on the CME, COMEX, NYMEX and CBOT, on around twenty platforms including NinjaTrader, Tradovate and TradingView. A training library is included.</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>« Country ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>ceo_fondateur</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Osvaldo Guimarães</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Futures</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Index futures, Energy futures, Metals futures, Agricultural futures, Currency futures, Micro futures</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>(vide — non confirmees)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>plateformes</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>moyens_paiement</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>methodes_retrait</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Rise, Deel, Bayzat, Direct crypto</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>prestataire_retrait</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>levier_statut</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>styles_trading</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>(vide — absent du releve)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>meta_description</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Futures prop firm: Trader Career Path from $25K to $200K, end-of-day drawdown in the evaluation, split up to 80%, weekly payouts. Rules and pitfalls.</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>flux_donnees</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -7444,11 +7444,7 @@
       <c r="E3" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="F3" s="17" t="n"/>
       <c r="G3" s="17" t="inlineStr">
         <is>
           <t>subscription</t>
@@ -7493,7 +7489,11 @@
       <c r="E4" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="F4" s="16" t="n"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
           <t>subscription</t>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Day 4 · TCP25 -60%</t>
+          <t>Day 4 · TCP25 + no fee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60% off the TCP25 today, activation fee waived.</t>
+          <t>50% off every plan today, and 60% on the TCP25 — activation fee waived.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Day 6 · -60% 50K</t>
+          <t>Day 6 · 50K + free eval</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60% off the TCP50 or the Gauntlet Mini 50K, plus a free evaluation after your first payout.</t>
+          <t>50% off every plan today, and 60% on the TCP50 or the Gauntlet Mini 50K — plus a free evaluation after your first payout.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Day 8 · TCP100 -60%</t>
+          <t>Day 8 · TCP100 + $50 resets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60% off the TCP100 today, with resets at $50.</t>
+          <t>50% off every plan today, and 60% on the TCP100 — resets at $50.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Day 4 · TCP25 -60%</t>
+          <t>Day 4 · TCP25 + no fee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60% off the TCP25 today, activation fee waived.</t>
+          <t>50% off every plan today, and 60% on the TCP25 — activation fee waived.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Day 6 · -60% 50K</t>
+          <t>Day 6 · 50K + free eval</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60% off the TCP50 or the Gauntlet Mini 50K, plus a free evaluation after your first payout.</t>
+          <t>50% off every plan today, and 60% on the TCP50 or the Gauntlet Mini 50K — plus a free evaluation after your first payout.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Day 8 · TCP100 -60%</t>
+          <t>Day 8 · TCP100 + $50 resets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60% off the TCP100 today, with resets at $50.</t>
+          <t>50% off every plan today, and 60% on the TCP100 — resets at $50.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7444,11 +7444,7 @@
       <c r="E3" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="F3" s="17" t="n"/>
       <c r="G3" s="17" t="inlineStr">
         <is>
           <t>subscription</t>
@@ -7493,7 +7489,11 @@
       <c r="E4" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="F4" s="16" t="n"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
           <t>subscription</t>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>not_published</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1577,7 +1577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1976,6 +1976,36 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>not_published</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-28T05:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:59:00+00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Halloween · -60%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>60% off every evaluation and 50% off resets — both apply to your first two months of subscription, purchase date included.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>confirmed</t>
         </is>
       </c>
     </row>

--- a/data/firms/earn2trade.xlsx
+++ b/data/firms/earn2trade.xlsx
@@ -1512,6 +1512,11 @@
           <t>accroche</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>60% off every evaluation and 50% off resets — both apply to your first two months of subscription, purchase date included.</t>
+        </is>
+      </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
@@ -1524,6 +1529,9 @@
           <t>remise_campagne</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>60</v>
+      </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
@@ -1536,6 +1544,11 @@
           <t>campagne_fin</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:59:00+00:00</t>
+        </is>
+      </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
@@ -1546,6 +1559,11 @@
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>bonus</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>+50% off resets</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
